--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710439</v>
+        <v>127710430</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623677</v>
+        <v>623697</v>
       </c>
       <c r="R6" t="n">
-        <v>7023323</v>
+        <v>7023229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710430</v>
+        <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623697</v>
+        <v>623677</v>
       </c>
       <c r="R7" t="n">
-        <v>7023229</v>
+        <v>7023323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710429</v>
+        <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623664</v>
+        <v>623697</v>
       </c>
       <c r="R9" t="n">
-        <v>7023211</v>
+        <v>7023229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710435</v>
+        <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623749</v>
+        <v>623664</v>
       </c>
       <c r="R10" t="n">
-        <v>7023258</v>
+        <v>7023211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710431</v>
+        <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623697</v>
+        <v>623749</v>
       </c>
       <c r="R11" t="n">
-        <v>7023229</v>
+        <v>7023258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127710438</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710431</v>
+        <v>127710429</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623697</v>
+        <v>623664</v>
       </c>
       <c r="R9" t="n">
-        <v>7023229</v>
+        <v>7023211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710429</v>
+        <v>127710431</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623664</v>
+        <v>623697</v>
       </c>
       <c r="R10" t="n">
-        <v>7023211</v>
+        <v>7023229</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80158</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80158</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710429</v>
+        <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623664</v>
+        <v>623697</v>
       </c>
       <c r="R9" t="n">
-        <v>7023211</v>
+        <v>7023229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710431</v>
+        <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>98450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623697</v>
+        <v>623664</v>
       </c>
       <c r="R10" t="n">
-        <v>7023229</v>
+        <v>7023211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80158</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>80158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710431</v>
+        <v>127710429</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623697</v>
+        <v>623664</v>
       </c>
       <c r="R9" t="n">
-        <v>7023229</v>
+        <v>7023211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710429</v>
+        <v>127710435</v>
       </c>
       <c r="B10" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623664</v>
+        <v>623749</v>
       </c>
       <c r="R10" t="n">
-        <v>7023211</v>
+        <v>7023258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710435</v>
+        <v>127710431</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623749</v>
+        <v>623697</v>
       </c>
       <c r="R11" t="n">
-        <v>7023258</v>
+        <v>7023229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>80161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80158</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127710430</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127710429</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127710435</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127710431</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127710438</v>
       </c>
       <c r="B12" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80161</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>80167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127710430</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710429</v>
+        <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623664</v>
+        <v>623697</v>
       </c>
       <c r="R9" t="n">
-        <v>7023211</v>
+        <v>7023229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710435</v>
+        <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623749</v>
+        <v>623664</v>
       </c>
       <c r="R10" t="n">
-        <v>7023258</v>
+        <v>7023211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710431</v>
+        <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>79641</v>
+        <v>98467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623697</v>
+        <v>623749</v>
       </c>
       <c r="R11" t="n">
-        <v>7023229</v>
+        <v>7023258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>127710438</v>
       </c>
       <c r="B12" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>80167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80167</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710430</v>
+        <v>127710439</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623697</v>
+        <v>623677</v>
       </c>
       <c r="R6" t="n">
-        <v>7023229</v>
+        <v>7023323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710439</v>
+        <v>127710430</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623677</v>
+        <v>623697</v>
       </c>
       <c r="R7" t="n">
-        <v>7023323</v>
+        <v>7023229</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710431</v>
+        <v>127710429</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623697</v>
+        <v>623664</v>
       </c>
       <c r="R9" t="n">
-        <v>7023229</v>
+        <v>7023211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710429</v>
+        <v>127710435</v>
       </c>
       <c r="B10" t="n">
         <v>98468</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623664</v>
+        <v>623749</v>
       </c>
       <c r="R10" t="n">
-        <v>7023211</v>
+        <v>7023258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710435</v>
+        <v>127710431</v>
       </c>
       <c r="B11" t="n">
-        <v>98468</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623749</v>
+        <v>623697</v>
       </c>
       <c r="R11" t="n">
-        <v>7023258</v>
+        <v>7023229</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80167</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>80167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710439</v>
+        <v>127710430</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623677</v>
+        <v>623697</v>
       </c>
       <c r="R6" t="n">
-        <v>7023323</v>
+        <v>7023229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710430</v>
+        <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623697</v>
+        <v>623677</v>
       </c>
       <c r="R7" t="n">
-        <v>7023229</v>
+        <v>7023323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127710429</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127710435</v>
       </c>
       <c r="B10" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>80167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710429</v>
+        <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623664</v>
+        <v>623697</v>
       </c>
       <c r="R9" t="n">
-        <v>7023211</v>
+        <v>7023229</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710435</v>
+        <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623749</v>
+        <v>623664</v>
       </c>
       <c r="R10" t="n">
-        <v>7023258</v>
+        <v>7023211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710431</v>
+        <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>98470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623697</v>
+        <v>623749</v>
       </c>
       <c r="R11" t="n">
-        <v>7023229</v>
+        <v>7023258</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B3" t="n">
-        <v>80167</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>80170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710430</v>
+        <v>127710439</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623697</v>
+        <v>623677</v>
       </c>
       <c r="R6" t="n">
-        <v>7023229</v>
+        <v>7023323</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710439</v>
+        <v>127710430</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623677</v>
+        <v>623697</v>
       </c>
       <c r="R7" t="n">
-        <v>7023323</v>
+        <v>7023229</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91648</v>
+        <v>91656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127710438</v>
       </c>
       <c r="B12" t="n">
-        <v>80160</v>
+        <v>80163</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710437</v>
+        <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>80170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623693</v>
+        <v>623732</v>
       </c>
       <c r="R3" t="n">
-        <v>7023297</v>
+        <v>7023267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710436</v>
+        <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>80170</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623732</v>
+        <v>623693</v>
       </c>
       <c r="R4" t="n">
-        <v>7023267</v>
+        <v>7023297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127710432</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127710436</v>
       </c>
       <c r="B3" t="n">
-        <v>80170</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127710437</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127710433</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710439</v>
+        <v>127710430</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623677</v>
+        <v>623697</v>
       </c>
       <c r="R6" t="n">
-        <v>7023323</v>
+        <v>7023229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710430</v>
+        <v>127710439</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>98490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623697</v>
+        <v>623677</v>
       </c>
       <c r="R7" t="n">
-        <v>7023229</v>
+        <v>7023323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>127710434</v>
       </c>
       <c r="B8" t="n">
-        <v>91656</v>
+        <v>91667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127710431</v>
       </c>
       <c r="B9" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127710429</v>
       </c>
       <c r="B10" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127710435</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127710438</v>
       </c>
       <c r="B12" t="n">
-        <v>80163</v>
+        <v>80174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127710432</v>
+        <v>127710434</v>
       </c>
       <c r="B2" t="n">
-        <v>98490</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623692</v>
+        <v>623798</v>
       </c>
       <c r="R2" t="n">
-        <v>7023238</v>
+        <v>7023240</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,27 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127710436</v>
+        <v>127710430</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623732</v>
+        <v>623697</v>
       </c>
       <c r="R3" t="n">
-        <v>7023267</v>
+        <v>7023229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127710437</v>
+        <v>127710431</v>
       </c>
       <c r="B4" t="n">
-        <v>98490</v>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623693</v>
+        <v>623697</v>
       </c>
       <c r="R4" t="n">
-        <v>7023297</v>
+        <v>7023229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127710433</v>
+        <v>127710438</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623739</v>
+        <v>623693</v>
       </c>
       <c r="R5" t="n">
-        <v>7023239</v>
+        <v>7023297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,27 +1063,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127710430</v>
+        <v>127710436</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>80467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623697</v>
+        <v>623732</v>
       </c>
       <c r="R6" t="n">
-        <v>7023229</v>
+        <v>7023267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127710439</v>
+        <v>127710429</v>
       </c>
       <c r="B7" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623677</v>
+        <v>623664</v>
       </c>
       <c r="R7" t="n">
-        <v>7023323</v>
+        <v>7023211</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127710434</v>
+        <v>127710432</v>
       </c>
       <c r="B8" t="n">
-        <v>91667</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623798</v>
+        <v>623692</v>
       </c>
       <c r="R8" t="n">
-        <v>7023240</v>
+        <v>7023238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127710431</v>
+        <v>127710433</v>
       </c>
       <c r="B9" t="n">
-        <v>79661</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623697</v>
+        <v>623739</v>
       </c>
       <c r="R9" t="n">
-        <v>7023229</v>
+        <v>7023239</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127710429</v>
+        <v>127710435</v>
       </c>
       <c r="B10" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623664</v>
+        <v>623749</v>
       </c>
       <c r="R10" t="n">
-        <v>7023211</v>
+        <v>7023258</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127710435</v>
+        <v>127710437</v>
       </c>
       <c r="B11" t="n">
-        <v>98490</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623749</v>
+        <v>623693</v>
       </c>
       <c r="R11" t="n">
-        <v>7023258</v>
+        <v>7023297</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127710438</v>
+        <v>127710439</v>
       </c>
       <c r="B12" t="n">
-        <v>80174</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623693</v>
+        <v>623677</v>
       </c>
       <c r="R12" t="n">
-        <v>7023297</v>
+        <v>7023323</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 15666-2025 artfynd.xlsx
+++ b/artfynd/A 15666-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710430</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710431</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710438</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710436</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710429</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710432</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710433</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710435</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710437</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127710439</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>